--- a/mode_docx_gen/pmi_tokz/part/tofflvlgc/rblc1/LVCBRBLC1.xlsx
+++ b/mode_docx_gen/pmi_tokz/part/tofflvlgc/rblc1/LVCBRBLC1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\35. ЛО Т 35 Т\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_tokz\part\tofflvlgc\rblc1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="80">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Логика запрета АВР</t>
+  </si>
+  <si>
+    <t>alias</t>
   </si>
 </sst>
 </file>
@@ -293,7 +296,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -329,11 +332,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -343,6 +357,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -645,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -659,7 +676,7 @@
     <col min="28" max="28" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -750,8 +767,11 @@
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="5" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -843,7 +863,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -935,7 +955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1027,7 +1047,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
@@ -1119,7 +1139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -1211,7 +1231,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1303,7 +1323,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -1395,7 +1415,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
